--- a/data/trans_dic/IP37-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han trabajado anteriormente</t>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,41; 97,5</t>
+          <t>75,09; 97,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,94; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70,76; 100,0</t>
+          <t>72,73; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,87; 100,0</t>
+          <t>74,76; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,76; 96,66</t>
+          <t>74,27; 96,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,66; 100,0</t>
+          <t>85,25; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,73; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,36; 100,0</t>
+          <t>85,38; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,64; 95,5</t>
+          <t>78,99; 95,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90,86; 100,0</t>
+          <t>92,12; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,95; 100,0</t>
+          <t>87,15; 100,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,8; 100,0</t>
+          <t>81,53; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,11; 100,0</t>
+          <t>89,69; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,91; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,79; 94,02</t>
+          <t>62,4; 93,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,17; 100,0</t>
+          <t>81,95; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,28; 98,38</t>
+          <t>86,0; 98,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,76; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>73,76; 100,0</t>
+          <t>75,54; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,63; 98,87</t>
+          <t>88,77; 98,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,92; 98,25</t>
+          <t>90,22; 98,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98,4; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,78; 95,52</t>
+          <t>77,07; 95,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,27; 96,1</t>
+          <t>64,94; 95,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,04; 100,0</t>
+          <t>87,81; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,7; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,06; 94,52</t>
+          <t>52,05; 94,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,07; 93,65</t>
+          <t>75,94; 95,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,98; 95,11</t>
+          <t>78,16; 95,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,22; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,78; 100,0</t>
+          <t>76,01; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,49; 92,25</t>
+          <t>77,06; 93,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,97; 96,3</t>
+          <t>85,94; 96,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97,45; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,77; 97,08</t>
+          <t>72,86; 96,89</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,54; 98,27</t>
+          <t>89,65; 98,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,37; 98,28</t>
+          <t>91,98; 98,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,62; 100,0</t>
+          <t>97,21; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,43; 99,47</t>
+          <t>92,17; 99,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,72; 97,65</t>
+          <t>89,84; 98,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,51; 97,78</t>
+          <t>91,55; 97,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,48; 99,39</t>
+          <t>93,97; 99,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,79; 98,13</t>
+          <t>88,39; 97,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,69; 97,17</t>
+          <t>91,65; 97,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,31; 97,67</t>
+          <t>93,21; 97,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96,94; 99,68</t>
+          <t>97,15; 99,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,43; 98,08</t>
+          <t>92,17; 98,15</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>93,0; 100,0</t>
+          <t>92,06; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,21; 99,21</t>
+          <t>92,19; 99,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,54; 100,0</t>
+          <t>97,08; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,41; 97,53</t>
+          <t>86,0; 97,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,23; 98,99</t>
+          <t>91,12; 99,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,32; 99,29</t>
+          <t>93,7; 99,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,4; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,55; 98,2</t>
+          <t>82,06; 98,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93,71; 98,9</t>
+          <t>93,82; 98,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94,56; 98,8</t>
+          <t>94,44; 98,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98,22; 100,0</t>
+          <t>98,39; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,26; 97,24</t>
+          <t>88,29; 96,85</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,54</t>
+          <t>1,99; 11,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 14,17</t>
+          <t>2,51; 14,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,87</t>
+          <t>2,92; 12,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,62</t>
+          <t>1,24; 10,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,1</t>
+          <t>2,23; 11,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 15,68</t>
+          <t>4,15; 15,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,59</t>
+          <t>1,07; 10,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,31</t>
+          <t>3,12; 9,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,57</t>
+          <t>4,15; 12,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,8</t>
+          <t>2,72; 9,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,23</t>
+          <t>0,57; 4,91</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,36; 75,57</t>
+          <t>67,09; 75,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,56; 87,18</t>
+          <t>80,38; 87,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,81; 86,78</t>
+          <t>79,05; 86,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,72; 79,56</t>
+          <t>64,0; 79,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,41; 76,19</t>
+          <t>66,84; 75,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,53; 83,3</t>
+          <t>76,25; 82,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,81; 83,71</t>
+          <t>76,75; 84,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>64,03; 74,79</t>
+          <t>63,63; 75,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68,36; 74,6</t>
+          <t>68,4; 74,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79,7; 84,06</t>
+          <t>79,61; 84,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,52; 84,27</t>
+          <t>79,24; 84,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,79; 75,48</t>
+          <t>65,27; 75,21</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>16122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20689</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17627</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13599</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16615</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18055</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20596</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22095</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>32737</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>38744</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38223</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>35694</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17423; 22566</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10828; 14888</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13501; 18060</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15005; 19533</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18188; 21335</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>29186; 34182</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>34287; 41337</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>35893; 38962</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>32230; 36983</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24285</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40367</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16179</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21294</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37357</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39203</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17047</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>45579</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>73599</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>79569</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>33227</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>20833; 25553</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>33691; 37563</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12187; 18269</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17979; 21938</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>34233; 39163</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13574; 17969</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>42159; 46954</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>69802; 76052</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>28899; 35980</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>14405</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22778</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27081</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27063</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>16801</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>41485</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66235</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>49841</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27702</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11042; 16307</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26930; 30668</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7109; 12872</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23638; 29751</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31993; 38941</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13424; 17661</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>37089; 44861</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>61533; 68966</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>22821; 30347</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>69692</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>115774</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108614</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90070</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73409</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>116486</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94077</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>64516</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>143101</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>232260</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>202690</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>154585</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>65820; 72123</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>110974; 118551</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106172; 109222</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>85573; 92323</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>69458; 75956</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>111646; 119308</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>90237; 95438</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>60316; 66838</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>138153; 146661</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>226136; 236664</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>199387; 204619</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>148457; 158096</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>55832</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>93571</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>83201</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46295</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58728</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90727</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84741</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>114561</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>184297</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>167942</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>100684</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>52591; 57128</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>89157; 95859</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81349; 83798</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>42619; 48358</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>55316; 60103</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>87005; 92196</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>47466; 56900</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>110557; 116555</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>179015; 187313</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>165825; 168539</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>94825; 104011</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3966</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3571</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2783</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7837</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8643</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2783</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1396; 8252</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1213; 6880</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1664; 7176</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>812; 6876</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1570; 7916</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2668; 10179</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>704; 6919</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>4388; 13046</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>4680; 13991</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3337; 11636</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>760; 6519</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>184300</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>299556</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>276157</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>179825</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>201000</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>174851</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>385300</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>603779</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>544632</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>354675</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>173979; 195315</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>287082; 310966</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>261540; 286229</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>163703; 202932</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>186872; 211398</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>289809; 315153</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>256438; 280760</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>159916; 188770</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>368608; 402406</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>586970; 620445</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>526878; 559849</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>330986; 381394</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP37-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Clase-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,09; 97,25</t>
+          <t>74,36; 97,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,22 +732,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72,73; 100,0</t>
+          <t>70,48; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,76; 100,0</t>
+          <t>73,16; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,27; 96,68</t>
+          <t>71,33; 96,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,25; 100,0</t>
+          <t>81,98; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,38; 100,0</t>
+          <t>87,2; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,99; 95,23</t>
+          <t>79,84; 95,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,12; 100,0</t>
+          <t>89,75; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,15; 100,0</t>
+          <t>86,75; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,53; 100,0</t>
+          <t>83,55; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,69; 100,0</t>
+          <t>89,38; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,4; 93,55</t>
+          <t>65,7; 93,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,95; 100,0</t>
+          <t>84,94; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,0; 98,39</t>
+          <t>85,84; 98,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,54; 100,0</t>
+          <t>75,3; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,77; 98,87</t>
+          <t>88,82; 98,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,22; 98,3</t>
+          <t>89,91; 98,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,07; 95,95</t>
+          <t>77,71; 95,65</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,94; 95,91</t>
+          <t>66,91; 96,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,81; 100,0</t>
+          <t>87,54; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,05; 94,23</t>
+          <t>53,2; 94,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,94; 95,57</t>
+          <t>75,73; 95,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,16; 95,13</t>
+          <t>78,02; 95,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,01; 100,0</t>
+          <t>74,67; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,06; 93,21</t>
+          <t>77,02; 92,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,94; 96,32</t>
+          <t>86,36; 96,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72,86; 96,89</t>
+          <t>73,54; 97,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,65; 98,23</t>
+          <t>88,91; 97,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,98; 98,25</t>
+          <t>92,01; 98,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,21; 100,0</t>
+          <t>97,02; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,17; 99,44</t>
+          <t>92,01; 99,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,84; 98,24</t>
+          <t>89,34; 97,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55; 97,83</t>
+          <t>91,49; 97,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,97; 99,39</t>
+          <t>94,58; 99,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,39; 97,95</t>
+          <t>88,74; 98,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,65; 97,3</t>
+          <t>91,32; 97,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,21; 97,55</t>
+          <t>93,18; 97,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97,15; 99,69</t>
+          <t>96,92; 99,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,17; 98,15</t>
+          <t>92,63; 98,45</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,06; 100,0</t>
+          <t>92,95; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,19; 99,12</t>
+          <t>92,15; 99,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,08; 100,0</t>
+          <t>95,73; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,0; 97,58</t>
+          <t>86,29; 98,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,12; 99,0</t>
+          <t>91,22; 99,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,7; 99,29</t>
+          <t>93,69; 99,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,06; 98,37</t>
+          <t>82,0; 98,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93,82; 98,91</t>
+          <t>94,22; 98,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94,44; 98,81</t>
+          <t>94,49; 98,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98,39; 100,0</t>
+          <t>98,23; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,29; 96,85</t>
+          <t>88,09; 97,14</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 11,77</t>
+          <t>1,97; 11,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,22</t>
+          <t>2,54; 14,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,58</t>
+          <t>2,22; 12,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,53</t>
+          <t>1,08; 10,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,24</t>
+          <t>1,92; 11,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,82</t>
+          <t>4,0; 15,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,53</t>
+          <t>1,08; 9,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,28</t>
+          <t>2,79; 9,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,41</t>
+          <t>4,17; 12,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,48</t>
+          <t>2,51; 8,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,91</t>
+          <t>0,57; 5,08</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>67,09; 75,32</t>
+          <t>66,17; 75,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,38; 87,06</t>
+          <t>80,71; 87,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,05; 86,52</t>
+          <t>79,96; 86,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64,0; 79,34</t>
+          <t>62,97; 78,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,84; 75,61</t>
+          <t>67,68; 76,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,25; 82,91</t>
+          <t>76,53; 83,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,75; 84,03</t>
+          <t>76,18; 83,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,63; 75,11</t>
+          <t>63,77; 74,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68,4; 74,67</t>
+          <t>68,27; 74,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79,61; 84,15</t>
+          <t>79,35; 84,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,24; 84,19</t>
+          <t>79,14; 84,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,27; 75,21</t>
+          <t>65,07; 74,74</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17423; 22566</t>
+          <t>17255; 22514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,22 +1942,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10828; 14888</t>
+          <t>10493; 14888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13501; 18060</t>
+          <t>13212; 18060</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15005; 19533</t>
+          <t>14411; 19531</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18188; 21335</t>
+          <t>17490; 21335</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29186; 34182</t>
+          <t>29808; 34182</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34287; 41337</t>
+          <t>34657; 41363</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35893; 38962</t>
+          <t>34970; 38962</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32230; 36983</t>
+          <t>32083; 36983</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20833; 25553</t>
+          <t>21349; 25553</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33691; 37563</t>
+          <t>33575; 37563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12187; 18269</t>
+          <t>12831; 18292</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17979; 21938</t>
+          <t>18634; 21938</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34233; 39163</t>
+          <t>34169; 39117</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13574; 17969</t>
+          <t>13531; 17969</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42159; 46954</t>
+          <t>42184; 46960</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69802; 76052</t>
+          <t>69561; 76016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28899; 35980</t>
+          <t>29139; 35867</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11042; 16307</t>
+          <t>11377; 16330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26930; 30668</t>
+          <t>26847; 30668</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7109; 12872</t>
+          <t>7267; 12913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23638; 29751</t>
+          <t>23574; 29745</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31993; 38941</t>
+          <t>31935; 38903</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13424; 17661</t>
+          <t>13187; 17661</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37089; 44861</t>
+          <t>37071; 44723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61533; 68966</t>
+          <t>61836; 68965</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22821; 30347</t>
+          <t>23034; 30422</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65820; 72123</t>
+          <t>65276; 71621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>110974; 118551</t>
+          <t>111011; 118540</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106172; 109222</t>
+          <t>105964; 109222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85573; 92323</t>
+          <t>85424; 92395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69458; 75956</t>
+          <t>69077; 75514</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111646; 119308</t>
+          <t>111573; 119357</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90237; 95438</t>
+          <t>90819; 95442</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60316; 66838</t>
+          <t>60552; 66885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>138153; 146661</t>
+          <t>137649; 146768</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>226136; 236664</t>
+          <t>226072; 236824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>199387; 204619</t>
+          <t>198933; 204564</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>148457; 158096</t>
+          <t>149205; 158574</t>
         </is>
       </c>
     </row>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>52591; 57128</t>
+          <t>53103; 57128</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89157; 95859</t>
+          <t>89114; 95937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81349; 83798</t>
+          <t>80217; 83798</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42619; 48358</t>
+          <t>42766; 48578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55316; 60103</t>
+          <t>55382; 60101</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87005; 92196</t>
+          <t>87000; 92192</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2794,27 +2794,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47466; 56900</t>
+          <t>47431; 56864</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110557; 116555</t>
+          <t>111033; 116561</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>179015; 187313</t>
+          <t>179119; 187298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165825; 168539</t>
+          <t>165555; 168539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94825; 104011</t>
+          <t>94603; 104324</t>
         </is>
       </c>
     </row>
@@ -2967,37 +2967,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1396; 8252</t>
+          <t>1378; 8266</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1213; 6880</t>
+          <t>1226; 7084</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1664; 7176</t>
+          <t>1269; 6963</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>812; 6876</t>
+          <t>708; 6782</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1570; 7916</t>
+          <t>1349; 7999</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2668; 10179</t>
+          <t>2575; 10243</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>704; 6919</t>
+          <t>708; 6406</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3007,22 +3007,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4388; 13046</t>
+          <t>3925; 13372</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4680; 13991</t>
+          <t>4705; 13933</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3337; 11636</t>
+          <t>3086; 10886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>760; 6519</t>
+          <t>756; 6749</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>173979; 195315</t>
+          <t>171603; 195323</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>287082; 310966</t>
+          <t>288285; 310846</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>261540; 286229</t>
+          <t>264542; 286985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163703; 202932</t>
+          <t>161076; 201949</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>186872; 211398</t>
+          <t>189211; 212859</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>289809; 315153</t>
+          <t>290883; 316497</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>256438; 280760</t>
+          <t>254529; 279497</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>159916; 188770</t>
+          <t>160267; 187799</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>368608; 402406</t>
+          <t>367895; 401687</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>586970; 620445</t>
+          <t>585044; 619973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>526878; 559849</t>
+          <t>526225; 560899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>330986; 381394</t>
+          <t>329948; 379018</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP37-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>89,37%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>89,16%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75,87; 100,0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71,76; 96,66</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82,66; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>74,36; 97,03</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70,48; 100,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>73,16; 100,0</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,33; 96,68</t>
+          <t>76,41; 97,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,98; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,97; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,2; 100,0</t>
+          <t>86,36; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,84; 95,29</t>
+          <t>79,64; 95,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,75; 100,0</t>
+          <t>90,86; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,75; 100,0</t>
+          <t>84,79; 100,0</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>95,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,55; 100,0</t>
+          <t>83,17; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,38; 100,0</t>
+          <t>86,28; 98,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,7; 93,67</t>
+          <t>73,26; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,94; 100,0</t>
+          <t>82,8; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,84; 98,27</t>
+          <t>89,11; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,3; 100,0</t>
+          <t>65,8; 94,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,82; 98,88</t>
+          <t>88,63; 98,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,91; 98,25</t>
+          <t>89,92; 98,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,71; 95,65</t>
+          <t>75,91; 95,26</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94,81%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>84,72%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>97,83%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>81,22%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,91; 96,04</t>
+          <t>74,07; 93,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,54; 100,0</t>
+          <t>78,98; 95,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,2; 94,54</t>
+          <t>74,79; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,73; 95,55</t>
+          <t>65,27; 96,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,02; 95,04</t>
+          <t>89,04; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,67; 100,0</t>
+          <t>55,23; 94,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,02; 92,92</t>
+          <t>76,49; 92,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86,36; 96,32</t>
+          <t>85,97; 96,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,54; 97,13</t>
+          <t>74,08; 97,07</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>94,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>95,95%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,91; 97,55</t>
+          <t>89,72; 97,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,01; 98,25</t>
+          <t>91,51; 97,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,02; 100,0</t>
+          <t>94,48; 99,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,01; 99,52</t>
+          <t>87,22; 98,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,34; 97,67</t>
+          <t>90,54; 98,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,49; 97,87</t>
+          <t>92,37; 98,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,58; 99,39</t>
+          <t>96,62; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,74; 98,02</t>
+          <t>88,29; 98,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,32; 97,37</t>
+          <t>91,69; 97,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,18; 97,61</t>
+          <t>93,31; 97,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96,92; 99,67</t>
+          <t>96,94; 99,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,63; 98,45</t>
+          <t>90,41; 97,29</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>97,73%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96,75%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,95; 100,0</t>
+          <t>90,23; 98,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,15; 99,2</t>
+          <t>93,32; 99,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,73; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,29; 98,02</t>
+          <t>82,91; 98,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,22; 99,0</t>
+          <t>93,0; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,69; 99,29</t>
+          <t>92,21; 99,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,54; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,0; 98,31</t>
+          <t>84,73; 97,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94,22; 98,92</t>
+          <t>93,71; 98,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94,49; 98,8</t>
+          <t>94,56; 98,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98,23; 100,0</t>
+          <t>98,22; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,09; 97,14</t>
+          <t>86,94; 97,1</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,66%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,78%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6,26%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,79</t>
+          <t>2,03; 11,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 14,64</t>
+          <t>4,13; 15,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,2</t>
+          <t>1,08; 10,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,36</t>
+          <t>1,96; 11,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,92</t>
+          <t>2,63; 14,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,74</t>
+          <t>2,16; 11,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,22; 11,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,52</t>
+          <t>3,03; 9,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,36</t>
+          <t>4,16; 12,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,87</t>
+          <t>2,63; 8,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,08</t>
+          <t>0,56; 5,95</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71,9%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>71,07%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>83,87%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>83,47%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71,9%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,36%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,17; 75,32</t>
+          <t>67,41; 76,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,71; 87,03</t>
+          <t>76,53; 83,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,96; 86,74</t>
+          <t>76,81; 83,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,97; 78,95</t>
+          <t>62,85; 73,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,68; 76,14</t>
+          <t>66,36; 75,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,53; 83,27</t>
+          <t>80,56; 87,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,18; 83,66</t>
+          <t>79,81; 86,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,77; 74,73</t>
+          <t>58,75; 70,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68,27; 74,54</t>
+          <t>68,36; 74,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79,35; 84,09</t>
+          <t>79,7; 84,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,14; 84,35</t>
+          <t>79,52; 84,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,07; 74,74</t>
+          <t>62,84; 70,79</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16615</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18055</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20596</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16494</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>16122</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>20689</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>17627</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13599</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16615</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18055</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20596</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>27870</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13702; 18060</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14497; 19529</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17636; 21335</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17255; 22514</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10493; 14888</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13212; 18060</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14411; 19531</t>
+          <t>17731; 22624</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17490; 21335</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8653; 12732</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29808; 34182</t>
+          <t>29520; 34182</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34657; 41363</t>
+          <t>34568; 41454</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34970; 38962</t>
+          <t>35401; 38962</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32083; 36983</t>
+          <t>24780; 29225</t>
         </is>
       </c>
     </row>
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21294</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37357</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39203</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16498</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24285</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>36241</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>40367</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16179</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21294</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37357</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39203</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>32875</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21349; 25553</t>
+          <t>18247; 21938</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33575; 37563</t>
+          <t>34343; 39161</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12831; 18292</t>
+          <t>12749; 17403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18634; 21938</t>
+          <t>21158; 25553</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34169; 39117</t>
+          <t>33473; 37563</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13531; 17969</t>
+          <t>13065; 18687</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42184; 46960</t>
+          <t>42090; 46956</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69561; 76016</t>
+          <t>69570; 76015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29139; 35867</t>
+          <t>28283; 35493</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27081</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27063</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15379</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>14405</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>30003</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>22778</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10900</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27081</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36232</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27063</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>26785</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11377; 16330</t>
+          <t>23056; 29152</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26847; 30668</t>
+          <t>32327; 38933</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7267; 12913</t>
+          <t>12131; 16220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23574; 29745</t>
+          <t>11098; 16339</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31935; 38903</t>
+          <t>27307; 30668</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13187; 17661</t>
+          <t>7756; 13314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37071; 44723</t>
+          <t>36815; 44403</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61836; 68965</t>
+          <t>61555; 68950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23034; 30422</t>
+          <t>22420; 29379</t>
         </is>
       </c>
     </row>
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73409</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>116486</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94077</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58536</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>69692</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>115774</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>108614</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90070</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73409</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>116486</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94077</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>57206</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>154585</t>
+          <t>115742</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65276; 71621</t>
+          <t>69365; 75500</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>111011; 118540</t>
+          <t>111600; 119252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105964; 109222</t>
+          <t>90727; 95441</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85424; 92395</t>
+          <t>54045; 60786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69077; 75514</t>
+          <t>66476; 72148</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111573; 119357</t>
+          <t>111445; 118578</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90819; 95442</t>
+          <t>105533; 109222</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60552; 66885</t>
+          <t>53032; 59274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>137649; 146768</t>
+          <t>138206; 146478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>226072; 236824</t>
+          <t>226388; 236967</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198933; 204564</t>
+          <t>198961; 204582</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>149205; 158574</t>
+          <t>110325; 118728</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58728</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>90727</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84741</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>50833</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>55832</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>93571</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>83201</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>46295</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>58728</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90727</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84741</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54391</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>100684</t>
+          <t>95450</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53103; 57128</t>
+          <t>54776; 60094</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89114; 95937</t>
+          <t>86654; 92198</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80217; 83798</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42766; 48578</t>
+          <t>44759; 53090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55382; 60101</t>
+          <t>53128; 57128</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87000; 92192</t>
+          <t>89172; 95942</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80898; 83798</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47431; 56864</t>
+          <t>40694; 46728</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111033; 116561</t>
+          <t>110428; 116541</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>179119; 187298</t>
+          <t>179252; 187294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165555; 168539</t>
+          <t>165547; 168539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94603; 104324</t>
+          <t>88685; 99054</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3966</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3278</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3571</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2783</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2796</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>3094</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1378; 8266</t>
+          <t>1428; 7818</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1226; 7084</t>
+          <t>2657; 10092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1269; 6963</t>
+          <t>711; 6960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>708; 6782</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1349; 7999</t>
+          <t>1375; 8087</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2575; 10243</t>
+          <t>1271; 6855</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>708; 6406</t>
+          <t>1233; 6773</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>811; 7789</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3925; 13372</t>
+          <t>4251; 13089</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4705; 13933</t>
+          <t>4687; 14165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3086; 10886</t>
+          <t>3223; 10804</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>756; 6749</t>
+          <t>736; 7782</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>213</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>201000</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>157739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>184300</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>276157</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>179825</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>201000</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>174851</t>
+          <t>144077</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>354675</t>
+          <t>301816</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>171603; 195323</t>
+          <t>188465; 213015</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>288285; 310846</t>
+          <t>290894; 316614</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>264542; 286985</t>
+          <t>256617; 279684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161076; 201949</t>
+          <t>144772; 169915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>189211; 212859</t>
+          <t>172099; 195968</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>290883; 316497</t>
+          <t>287752; 311397</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>254529; 279497</t>
+          <t>264028; 287099</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>160267; 187799</t>
+          <t>130024; 155999</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>367895; 401687</t>
+          <t>368368; 402007</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>585044; 619973</t>
+          <t>587626; 619723</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>526225; 560899</t>
+          <t>528736; 560368</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>329948; 379018</t>
+          <t>283822; 319731</t>
         </is>
       </c>
     </row>
